--- a/output/graficos_dimensiones/comunal_d_env_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:53</t>
+    <t xml:space="preserve">2026-08-17 18:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 18:06</t>
+    <t xml:space="preserve">2026-09-01 17:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:51</t>
+    <t xml:space="preserve">2026-09-06 22:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
